--- a/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D8B9E4-2105-45EA-BEBF-EE6E0FB550D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AC3F13-1997-46E5-B135-59E523FA5802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="369">
   <si>
     <t>Non-Tariff Notifications : 2024</t>
   </si>
@@ -1111,6 +1111,24 @@
   </si>
   <si>
     <t>53/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>59/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>60/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>61/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>The Sea Cargo Manifest and Transshipment (Second Amendment) Regulations, 2026</t>
+  </si>
+  <si>
+    <t>62/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>Customs Tariff (Determination of Origin of Goods under the Comprehensive Economic and Trade Agreement between India and the United Kingdom of Great Britain &amp; Northern Ireland) Rules, 2026</t>
   </si>
 </sst>
 </file>
@@ -1142,7 +1160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1152,6 +1170,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1168,7 +1198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1189,6 +1219,19 @@
     <xf numFmtId="15" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1470,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1504,45 +1547,45 @@
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="B6" s="9">
-        <v>46195</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>357</v>
+    <row r="6" spans="1:3" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="B6" s="16">
+        <v>46206</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="B7" s="9">
-        <v>46191</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>356</v>
+      <c r="A7" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B7" s="12">
+        <v>46204</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="B8" s="9">
-        <v>46189</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>353</v>
+      <c r="A8" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="B8" s="12">
+        <v>46203</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B9" s="9">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>154</v>
@@ -1550,120 +1593,120 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46195</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B11" s="9">
+        <v>46191</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B12" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B13" s="9">
+        <v>46188</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B14" s="9">
         <v>46184</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="C14" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B15" s="9">
         <v>46184</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C15" s="10" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B16" s="9">
         <v>46182</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B17" s="9">
         <v>46178</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B18" s="9">
         <v>46178</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C18" s="10" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>346</v>
-      </c>
-      <c r="B15" s="3">
-        <v>46171</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>347</v>
-      </c>
-      <c r="B16" s="3">
-        <v>46161</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>348</v>
-      </c>
-      <c r="B17" s="3">
-        <v>46157</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>349</v>
-      </c>
-      <c r="B18" s="3">
-        <v>46150</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B19" s="3">
-        <v>46148</v>
+        <v>46171</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>341</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="B20" s="3">
-        <v>46142</v>
+        <v>46161</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>154</v>
@@ -1671,43 +1714,43 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="B21" s="3">
-        <v>46136</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>163</v>
+        <v>46157</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="B22" s="3">
-        <v>46132</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>46150</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="B23" s="3">
-        <v>46128</v>
+        <v>46148</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B24" s="3">
-        <v>46127</v>
+        <v>46142</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>154</v>
@@ -1715,98 +1758,98 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B25" s="3">
-        <v>46118</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>315</v>
+        <v>46136</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B26" s="3">
-        <v>46114</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46132</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>316</v>
       </c>
       <c r="B27" s="3">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="B28" s="3">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>312</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B29" s="3">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>171</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B30" s="3">
-        <v>46111</v>
+        <v>46114</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>313</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>327</v>
+        <v>191</v>
       </c>
       <c r="B31" s="3">
-        <v>46105</v>
+        <v>46112</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>328</v>
+        <v>192</v>
       </c>
       <c r="B32" s="3">
-        <v>46101</v>
+        <v>46112</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B33" s="3">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>171</v>
@@ -1814,76 +1857,76 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B34" s="3">
-        <v>46100</v>
+        <v>46111</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>154</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="B35" s="3">
-        <v>46097</v>
+        <v>46105</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>266</v>
+        <v>328</v>
       </c>
       <c r="B36" s="3">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>154</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>329</v>
       </c>
       <c r="B37" s="3">
-        <v>46077</v>
+        <v>46101</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="B38" s="3">
-        <v>46071</v>
+        <v>46100</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>304</v>
+        <v>265</v>
       </c>
       <c r="B39" s="3">
-        <v>46069</v>
+        <v>46097</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>176</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>305</v>
+        <v>266</v>
       </c>
       <c r="B40" s="3">
-        <v>46066</v>
+        <v>46094</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>154</v>
@@ -1891,10 +1934,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>306</v>
+        <v>201</v>
       </c>
       <c r="B41" s="3">
-        <v>46059</v>
+        <v>46077</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>154</v>
@@ -1902,210 +1945,254 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B42" s="3">
-        <v>46058</v>
+        <v>46071</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B43" s="3">
-        <v>46056</v>
-      </c>
-      <c r="C43" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>286</v>
+        <v>46069</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>305</v>
       </c>
       <c r="B44" s="3">
-        <v>46056</v>
-      </c>
-      <c r="C44" t="s">
-        <v>286</v>
+        <v>46066</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="B45" s="3">
-        <v>46055</v>
-      </c>
-      <c r="C45" t="s">
+        <v>46059</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="B46" s="3">
-        <v>46054</v>
-      </c>
-      <c r="C46" t="s">
-        <v>289</v>
+        <v>46058</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B47" s="3">
-        <v>46054</v>
+        <v>46056</v>
       </c>
       <c r="C47" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>292</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="B48" s="3">
-        <v>46054</v>
+        <v>46056</v>
       </c>
       <c r="C48" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B49" s="3">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C49" t="s">
-        <v>295</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B50" s="3">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="C50" t="s">
-        <v>154</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>331</v>
+        <v>290</v>
       </c>
       <c r="B51" s="3">
-        <v>46051</v>
+        <v>46054</v>
       </c>
       <c r="C51" t="s">
-        <v>154</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="B52" s="3">
-        <v>46049</v>
+        <v>46054</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>333</v>
+        <v>294</v>
       </c>
       <c r="B53" s="3">
-        <v>46044</v>
+        <v>46054</v>
       </c>
       <c r="C53" t="s">
-        <v>154</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>334</v>
+        <v>296</v>
       </c>
       <c r="B54" s="3">
-        <v>46037</v>
+        <v>46052</v>
       </c>
       <c r="C54" t="s">
-        <v>297</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B55" s="3">
-        <v>46037</v>
+        <v>46051</v>
       </c>
       <c r="C55" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B56" s="3">
-        <v>46037</v>
+        <v>46049</v>
       </c>
       <c r="C56" t="s">
-        <v>298</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B57" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="C57" t="s">
-        <v>299</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B58" s="3">
         <v>46037</v>
       </c>
       <c r="C58" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B59" s="3">
         <v>46037</v>
       </c>
       <c r="C59" t="s">
-        <v>301</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>336</v>
+      </c>
+      <c r="B60" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C60" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>337</v>
+      </c>
+      <c r="B61" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C61" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>338</v>
+      </c>
+      <c r="B62" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C62" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>339</v>
+      </c>
+      <c r="B63" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C63" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>340</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B64" s="3">
         <v>46035</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C64" t="s">
         <v>302</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AC3F13-1997-46E5-B135-59E523FA5802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9309DCE2-FA9B-4FBE-B9AD-63EB6463261D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="373">
   <si>
     <t>Non-Tariff Notifications : 2024</t>
   </si>
@@ -1129,6 +1129,18 @@
   </si>
   <si>
     <t>Customs Tariff (Determination of Origin of Goods under the Comprehensive Economic and Trade Agreement between India and the United Kingdom of Great Britain &amp; Northern Ireland) Rules, 2026</t>
+  </si>
+  <si>
+    <t>65/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>Appointment of Common Adjudicating Authority in the case of M/s. Inditech Trent Retails India Pvt. Ltd. IEC: 0509065597) – Consolidated Adjudication of Multiple Show Cause Notices arising from SVB Investigation Report No. Cus/SVB-DEL/164/2018-19 dated 27.12.2018</t>
+  </si>
+  <si>
+    <t>64/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>63/2026-Customs (N.T)</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1233,6 +1245,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1513,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1544,213 +1557,213 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B6" s="18">
+        <v>46219</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B7" s="18">
+        <v>46219</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>372</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46218</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B9" s="16">
         <v>46206</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C9" s="15" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B10" s="12">
         <v>46204</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C10" s="13" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B11" s="12">
         <v>46203</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="B9" s="9">
-        <v>46202</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="B10" s="9">
-        <v>46195</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="B11" s="9">
-        <v>46191</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>356</v>
+      <c r="C11" s="13" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B12" s="9">
-        <v>46189</v>
+        <v>46202</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>353</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B13" s="9">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>154</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" s="9">
+        <v>46191</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B16" s="9">
+        <v>46188</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B17" s="9">
         <v>46184</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="C17" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B18" s="9">
         <v>46184</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C18" s="10" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B19" s="9">
         <v>46182</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C19" s="10" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B20" s="9">
         <v>46178</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C20" s="10" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B21" s="9">
         <v>46178</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C21" s="10" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>346</v>
-      </c>
-      <c r="B19" s="3">
-        <v>46171</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>347</v>
-      </c>
-      <c r="B20" s="3">
-        <v>46161</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>348</v>
-      </c>
-      <c r="B21" s="3">
-        <v>46157</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B22" s="3">
-        <v>46150</v>
+        <v>46171</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B23" s="3">
-        <v>46148</v>
+        <v>46161</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>341</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="B24" s="3">
-        <v>46142</v>
+        <v>46157</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>154</v>
@@ -1758,186 +1771,186 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="B25" s="3">
-        <v>46136</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>163</v>
+        <v>46150</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="B26" s="3">
-        <v>46132</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>46148</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B27" s="3">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>317</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B28" s="3">
-        <v>46127</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>154</v>
+        <v>46136</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B29" s="3">
-        <v>46118</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46132</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B30" s="3">
-        <v>46114</v>
+        <v>46128</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>154</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
       <c r="B31" s="3">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>311</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>323</v>
       </c>
       <c r="B32" s="3">
-        <v>46112</v>
+        <v>46118</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B33" s="3">
-        <v>46111</v>
+        <v>46114</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>326</v>
+        <v>191</v>
       </c>
       <c r="B34" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>327</v>
+        <v>192</v>
       </c>
       <c r="B35" s="3">
-        <v>46105</v>
+        <v>46112</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B36" s="3">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>309</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B37" s="3">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>171</v>
+        <v>313</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B38" s="3">
-        <v>46100</v>
+        <v>46105</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>154</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>265</v>
+        <v>328</v>
       </c>
       <c r="B39" s="3">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="B40" s="3">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>330</v>
       </c>
       <c r="B41" s="3">
-        <v>46077</v>
+        <v>46100</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>154</v>
@@ -1945,32 +1958,32 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>303</v>
+        <v>265</v>
       </c>
       <c r="B42" s="3">
-        <v>46071</v>
+        <v>46097</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>304</v>
+        <v>266</v>
       </c>
       <c r="B43" s="3">
-        <v>46069</v>
+        <v>46094</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>305</v>
+        <v>201</v>
       </c>
       <c r="B44" s="3">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>154</v>
@@ -1978,142 +1991,142 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B45" s="3">
-        <v>46059</v>
+        <v>46071</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B46" s="3">
-        <v>46058</v>
+        <v>46069</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B47" s="3">
-        <v>46056</v>
-      </c>
-      <c r="C47" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>286</v>
+        <v>46066</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>306</v>
       </c>
       <c r="B48" s="3">
-        <v>46056</v>
-      </c>
-      <c r="C48" t="s">
-        <v>286</v>
+        <v>46059</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="B49" s="3">
-        <v>46055</v>
-      </c>
-      <c r="C49" t="s">
+        <v>46058</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="B50" s="3">
-        <v>46054</v>
+        <v>46056</v>
       </c>
       <c r="C50" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>290</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="B51" s="3">
-        <v>46054</v>
+        <v>46056</v>
       </c>
       <c r="C51" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B52" s="3">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C52" t="s">
-        <v>293</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B53" s="3">
         <v>46054</v>
       </c>
       <c r="C53" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B54" s="3">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="C54" t="s">
-        <v>154</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>331</v>
+        <v>292</v>
       </c>
       <c r="B55" s="3">
-        <v>46051</v>
+        <v>46054</v>
       </c>
       <c r="C55" t="s">
-        <v>154</v>
+        <v>293</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>332</v>
+        <v>294</v>
       </c>
       <c r="B56" s="3">
-        <v>46049</v>
+        <v>46054</v>
       </c>
       <c r="C56" t="s">
-        <v>154</v>
+        <v>295</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>333</v>
+        <v>296</v>
       </c>
       <c r="B57" s="3">
-        <v>46044</v>
+        <v>46052</v>
       </c>
       <c r="C57" t="s">
         <v>154</v>
@@ -2121,78 +2134,111 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B58" s="3">
-        <v>46037</v>
+        <v>46051</v>
       </c>
       <c r="C58" t="s">
-        <v>297</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B59" s="3">
-        <v>46037</v>
+        <v>46049</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B60" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="C60" t="s">
-        <v>298</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B61" s="3">
         <v>46037</v>
       </c>
       <c r="C61" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B62" s="3">
         <v>46037</v>
       </c>
       <c r="C62" t="s">
-        <v>300</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B63" s="3">
         <v>46037</v>
       </c>
       <c r="C63" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>337</v>
+      </c>
+      <c r="B64" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C64" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>338</v>
+      </c>
+      <c r="B65" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C65" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>339</v>
+      </c>
+      <c r="B66" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C66" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>340</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B67" s="3">
         <v>46035</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C67" t="s">
         <v>302</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9309DCE2-FA9B-4FBE-B9AD-63EB6463261D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81650BE-AC01-4C7E-B092-2CCF128D185C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="375">
   <si>
     <t>Non-Tariff Notifications : 2024</t>
   </si>
@@ -1141,6 +1141,12 @@
   </si>
   <si>
     <t>63/2026-Customs (N.T)</t>
+  </si>
+  <si>
+    <t>66/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>Notification of Udangudi port u/s. 7(1)(a) of Customs Act, 1962" and it was issued under Section 7(1)(a) of Customs Act, 1962.</t>
   </si>
 </sst>
 </file>
@@ -1526,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1562,208 +1568,208 @@
     </row>
     <row r="6" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B6" s="18">
+        <v>46223</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="B6" s="18">
-        <v>46219</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="B7" s="18">
         <v>46219</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B8" s="18">
+        <v>46219</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>372</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B9" s="3">
         <v>46218</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="C9" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B10" s="16">
         <v>46206</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C10" s="15" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="B10" s="12">
-        <v>46204</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B11" s="12">
+        <v>46204</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B12" s="12">
         <v>46203</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="B12" s="9">
-        <v>46202</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B13" s="9">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>357</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B14" s="9">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B15" s="9">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B16" s="9">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>154</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46188</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>354</v>
-      </c>
-      <c r="B17" s="9">
-        <v>46184</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>362</v>
       </c>
       <c r="B18" s="9">
         <v>46184</v>
       </c>
       <c r="C18" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B19" s="9">
+        <v>46184</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>355</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="B19" s="9">
-        <v>46182</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B20" s="9">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B21" s="9">
         <v>46178</v>
       </c>
       <c r="C21" s="10" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B22" s="9">
+        <v>46178</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>346</v>
-      </c>
-      <c r="B22" s="3">
-        <v>46171</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B23" s="3">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B24" s="3">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>154</v>
@@ -1771,10 +1777,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B25" s="3">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>154</v>
@@ -1782,208 +1788,208 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B26" s="3">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>341</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="B27" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>154</v>
+        <v>341</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B28" s="3">
-        <v>46136</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>163</v>
+        <v>46142</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>318</v>
+      </c>
+      <c r="B29" s="3">
+        <v>46136</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>321</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>46132</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C30" s="7" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>316</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <v>46128</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>317</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>322</v>
-      </c>
-      <c r="B31" s="3">
-        <v>46127</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B32" s="3">
-        <v>46118</v>
+        <v>46127</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>315</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B33" s="3">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>154</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>191</v>
+        <v>324</v>
       </c>
       <c r="B34" s="3">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>311</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B35" s="3">
         <v>46112</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>325</v>
+        <v>192</v>
       </c>
       <c r="B36" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B37" s="3">
         <v>46111</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>313</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B38" s="3">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B39" s="3">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B40" s="3">
         <v>46101</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>171</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B41" s="3">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>265</v>
+        <v>330</v>
       </c>
       <c r="B42" s="3">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>310</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B43" s="3">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>154</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="B44" s="3">
-        <v>46077</v>
+        <v>46094</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>154</v>
@@ -1991,43 +1997,43 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>201</v>
+      </c>
+      <c r="B45" s="3">
+        <v>46077</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>303</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B46" s="3">
         <v>46071</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="C46" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>304</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B47" s="3">
         <v>46069</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>305</v>
-      </c>
-      <c r="B47" s="3">
-        <v>46066</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B48" s="3">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>154</v>
@@ -2035,10 +2041,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B49" s="3">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>154</v>
@@ -2046,98 +2052,98 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>307</v>
+      </c>
+      <c r="B50" s="3">
+        <v>46058</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>308</v>
-      </c>
-      <c r="B50" s="3">
-        <v>46056</v>
-      </c>
-      <c r="C50" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="B51" s="3">
         <v>46056</v>
       </c>
       <c r="C51" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>287</v>
-      </c>
       <c r="B52" s="3">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B53" s="3">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C53" t="s">
-        <v>289</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B54" s="3">
         <v>46054</v>
       </c>
       <c r="C54" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B55" s="3">
         <v>46054</v>
       </c>
       <c r="C55" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B56" s="3">
         <v>46054</v>
       </c>
       <c r="C56" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B57" s="3">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="C57" t="s">
-        <v>154</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="B58" s="3">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="C58" t="s">
         <v>154</v>
@@ -2145,10 +2151,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B59" s="3">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="C59" t="s">
         <v>154</v>
@@ -2156,10 +2162,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B60" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="C60" t="s">
         <v>154</v>
@@ -2167,78 +2173,89 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B61" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="C61" t="s">
-        <v>297</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B62" s="3">
         <v>46037</v>
       </c>
       <c r="C62" t="s">
-        <v>10</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B63" s="3">
         <v>46037</v>
       </c>
       <c r="C63" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B64" s="3">
         <v>46037</v>
       </c>
       <c r="C64" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B65" s="3">
         <v>46037</v>
       </c>
       <c r="C65" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B66" s="3">
         <v>46037</v>
       </c>
       <c r="C66" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>339</v>
+      </c>
+      <c r="B67" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C67" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>340</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B68" s="3">
         <v>46035</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>302</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81650BE-AC01-4C7E-B092-2CCF128D185C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF3FB3E-D49C-4CF4-A12E-757817093BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="376">
   <si>
     <t>Non-Tariff Notifications : 2024</t>
   </si>
@@ -1147,6 +1147,9 @@
   </si>
   <si>
     <t>Notification of Udangudi port u/s. 7(1)(a) of Customs Act, 1962" and it was issued under Section 7(1)(a) of Customs Act, 1962.</t>
+  </si>
+  <si>
+    <t>68/2026-Customs (NT)</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1181,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1203,6 +1206,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1216,7 +1231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1243,7 +1258,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1251,13 +1265,27 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCCCFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1532,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1563,224 +1591,224 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="B6" s="21">
+        <v>46234</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B7" s="21">
         <v>46223</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="22" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>369</v>
-      </c>
-      <c r="B7" s="18">
-        <v>46219</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="B8" s="18">
         <v>46219</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="19" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="B9" s="18">
+        <v>46219</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B10" s="18">
         <v>46218</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="C10" s="19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B11" s="15">
         <v>46206</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="B11" s="12">
-        <v>46204</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B12" s="12">
+        <v>46204</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B13" s="12">
         <v>46203</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="B13" s="9">
-        <v>46202</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B14" s="9">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>357</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B15" s="9">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B16" s="9">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B17" s="9">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>154</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B18" s="9">
+        <v>46188</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>354</v>
-      </c>
-      <c r="B18" s="9">
-        <v>46184</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>362</v>
       </c>
       <c r="B19" s="9">
         <v>46184</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B20" s="9">
+        <v>46184</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>355</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="B20" s="9">
-        <v>46182</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B21" s="9">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B22" s="9">
         <v>46178</v>
       </c>
       <c r="C22" s="10" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46178</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>346</v>
-      </c>
-      <c r="B23" s="3">
-        <v>46171</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B24" s="3">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B25" s="3">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>154</v>
@@ -1788,10 +1816,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B26" s="3">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>154</v>
@@ -1799,208 +1827,208 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B27" s="3">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>341</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="B28" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>154</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B29" s="3">
-        <v>46136</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>163</v>
+        <v>46142</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>318</v>
+      </c>
+      <c r="B30" s="3">
+        <v>46136</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>321</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <v>46132</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C31" s="7" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>316</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B32" s="3">
         <v>46128</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>317</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>322</v>
-      </c>
-      <c r="B32" s="3">
-        <v>46127</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B33" s="3">
-        <v>46118</v>
+        <v>46127</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>315</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B34" s="3">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>154</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>324</v>
       </c>
       <c r="B35" s="3">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>311</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B36" s="3">
         <v>46112</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>325</v>
+        <v>192</v>
       </c>
       <c r="B37" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B38" s="3">
         <v>46111</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>313</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B39" s="3">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B40" s="3">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B41" s="3">
         <v>46101</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>171</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B42" s="3">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>265</v>
+        <v>330</v>
       </c>
       <c r="B43" s="3">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>310</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B44" s="3">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>154</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="B45" s="3">
-        <v>46077</v>
+        <v>46094</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>154</v>
@@ -2008,43 +2036,43 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>201</v>
+      </c>
+      <c r="B46" s="3">
+        <v>46077</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>303</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B47" s="3">
         <v>46071</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="C47" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>304</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B48" s="3">
         <v>46069</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>305</v>
-      </c>
-      <c r="B48" s="3">
-        <v>46066</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B49" s="3">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>154</v>
@@ -2052,10 +2080,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B50" s="3">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>154</v>
@@ -2063,98 +2091,98 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>307</v>
+      </c>
+      <c r="B51" s="3">
+        <v>46058</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>308</v>
-      </c>
-      <c r="B51" s="3">
-        <v>46056</v>
-      </c>
-      <c r="C51" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="B52" s="3">
         <v>46056</v>
       </c>
       <c r="C52" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>287</v>
-      </c>
       <c r="B53" s="3">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="C53" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B54" s="3">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C54" t="s">
-        <v>289</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B55" s="3">
         <v>46054</v>
       </c>
       <c r="C55" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B56" s="3">
         <v>46054</v>
       </c>
       <c r="C56" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B57" s="3">
         <v>46054</v>
       </c>
       <c r="C57" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B58" s="3">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>295</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="B59" s="3">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="C59" t="s">
         <v>154</v>
@@ -2162,10 +2190,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B60" s="3">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="C60" t="s">
         <v>154</v>
@@ -2173,10 +2201,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B61" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="C61" t="s">
         <v>154</v>
@@ -2184,78 +2212,89 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B62" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="C62" t="s">
-        <v>297</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B63" s="3">
         <v>46037</v>
       </c>
       <c r="C63" t="s">
-        <v>10</v>
+        <v>297</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B64" s="3">
         <v>46037</v>
       </c>
       <c r="C64" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B65" s="3">
         <v>46037</v>
       </c>
       <c r="C65" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B66" s="3">
         <v>46037</v>
       </c>
       <c r="C66" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B67" s="3">
         <v>46037</v>
       </c>
       <c r="C67" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>339</v>
+      </c>
+      <c r="B68" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C68" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>340</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B69" s="3">
         <v>46035</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C69" t="s">
         <v>302</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF3FB3E-D49C-4CF4-A12E-757817093BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFE0EF1-1D80-41E5-8BFC-B89345641771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -1181,7 +1181,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1218,6 +1218,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1231,7 +1237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1275,6 +1281,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1560,7 +1567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1568,19 +1575,19 @@
     <col min="3" max="3" width="149.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>285</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -1591,10 +1598,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>375</v>
       </c>
@@ -1604,8 +1611,9 @@
       <c r="C6" s="22" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="23"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>373</v>
       </c>
@@ -1615,8 +1623,9 @@
       <c r="C7" s="22" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="D7" s="23"/>
+    </row>
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>369</v>
       </c>
@@ -1626,8 +1635,9 @@
       <c r="C8" s="19" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="23"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>371</v>
       </c>
@@ -1637,8 +1647,9 @@
       <c r="C9" s="19" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="23"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>372</v>
       </c>
@@ -1648,8 +1659,9 @@
       <c r="C10" s="19" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="D10" s="23"/>
+    </row>
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>367</v>
       </c>
@@ -1659,8 +1671,9 @@
       <c r="C11" s="14" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="23"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>365</v>
       </c>
@@ -1670,8 +1683,9 @@
       <c r="C12" s="13" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="23"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>364</v>
       </c>
@@ -1681,8 +1695,9 @@
       <c r="C13" s="13" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="23"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>363</v>
       </c>
@@ -1692,8 +1707,9 @@
       <c r="C14" s="10" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" s="23"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>358</v>
       </c>
@@ -1704,7 +1720,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>359</v>
       </c>

--- a/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFE0EF1-1D80-41E5-8BFC-B89345641771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144CE5ED-ADCC-40CE-99E9-C821196886F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="379">
   <si>
     <t>Non-Tariff Notifications : 2024</t>
   </si>
@@ -1150,6 +1150,15 @@
   </si>
   <si>
     <t>68/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>67/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>"Notification of ICD at Umarwada, Ankleshwar, Bharuch, Gujarat u/s. 7(1)(aa) of Customs Act, 1962" and it was issued under Section 7(1)(aa) of Customs Act, 1962.</t>
+  </si>
+  <si>
+    <t>69/2026-Customs (N.T)</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1190,37 +1199,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor rgb="FFCCCCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1237,7 +1216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1248,40 +1227,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="15" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1567,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1575,19 +1539,19 @@
     <col min="3" max="3" width="149.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>285</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -1598,719 +1562,732 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B6" s="7">
+        <v>46244</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B7" s="10">
         <v>46234</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C7" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="23"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B8" s="7">
+        <v>46234</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B9" s="10">
         <v>46223</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C9" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="D7" s="23"/>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B10" s="10">
         <v>46219</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C10" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="D8" s="23"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B11" s="10">
         <v>46219</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C11" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D9" s="23"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B12" s="10">
         <v>46218</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D10" s="23"/>
-    </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="C12" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B13" s="10">
         <v>46206</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C13" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="D11" s="23"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B14" s="10">
         <v>46204</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="D12" s="23"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B15" s="10">
         <v>46203</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D13" s="23"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="C15" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B16" s="10">
         <v>46202</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="D14" s="23"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="C16" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B17" s="10">
         <v>46195</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B18" s="10">
         <v>46191</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B19" s="10">
         <v>46189</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B20" s="10">
         <v>46188</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="C20" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B21" s="10">
         <v>46184</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="C21" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B22" s="10">
         <v>46184</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B23" s="10">
         <v>46182</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B24" s="10">
         <v>46178</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B25" s="10">
         <v>46178</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C25" s="11" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B26" s="10">
         <v>46171</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C26" s="11" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B27" s="10">
         <v>46161</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C27" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B28" s="10">
         <v>46157</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="C28" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B29" s="10">
         <v>46150</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="C29" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B30" s="10">
         <v>46148</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C30" s="11" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B31" s="10">
         <v>46142</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="C31" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B32" s="10">
         <v>46136</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C32" s="13" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B33" s="10">
         <v>46132</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C33" s="14" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B34" s="10">
         <v>46128</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C34" s="11" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B35" s="10">
         <v>46127</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="C35" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B36" s="10">
         <v>46118</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C36" s="11" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B37" s="10">
         <v>46114</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="C37" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B38" s="10">
         <v>46112</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C38" s="11" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B39" s="10">
         <v>46112</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C39" s="11" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B40" s="10">
         <v>46111</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C40" s="11" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B41" s="10">
         <v>46111</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C41" s="11" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B42" s="10">
         <v>46105</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C42" s="11" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B43" s="10">
         <v>46101</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C43" s="11" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B44" s="10">
         <v>46101</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C44" s="11" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B45" s="10">
         <v>46100</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="C45" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B46" s="10">
         <v>46097</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C46" s="11" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B47" s="10">
         <v>46094</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="C47" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B48" s="10">
         <v>46077</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="C48" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B49" s="10">
         <v>46071</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="C49" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B50" s="10">
         <v>46069</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C50" s="11" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B51" s="10">
         <v>46066</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="C51" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B52" s="10">
         <v>46059</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="C52" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B53" s="10">
         <v>46058</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="C53" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B54" s="10">
         <v>46056</v>
       </c>
-      <c r="C52" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="C54" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B55" s="10">
         <v>46056</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C55" s="9" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B56" s="10">
         <v>46055</v>
       </c>
-      <c r="C54" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="C56" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B57" s="10">
         <v>46054</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C57" s="9" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B58" s="10">
         <v>46054</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C58" s="9" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B59" s="10">
         <v>46054</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C59" s="9" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B60" s="10">
         <v>46054</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C60" s="9" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B61" s="10">
         <v>46052</v>
       </c>
-      <c r="C59" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="C61" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B62" s="10">
         <v>46051</v>
       </c>
-      <c r="C60" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="C62" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B63" s="10">
         <v>46049</v>
       </c>
-      <c r="C61" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="C63" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B64" s="10">
         <v>46044</v>
       </c>
-      <c r="C62" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="C64" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B65" s="10">
         <v>46037</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C65" s="9" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B66" s="10">
         <v>46037</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C66" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B67" s="10">
         <v>46037</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C67" s="9" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B68" s="10">
         <v>46037</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C68" s="9" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B69" s="10">
         <v>46037</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C69" s="9" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B70" s="10">
         <v>46037</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C70" s="9" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B71" s="10">
         <v>46035</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C71" s="9" t="s">
         <v>302</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144CE5ED-ADCC-40CE-99E9-C821196886F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A067E975-9B83-44E5-919B-4F79D764ECDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="380">
   <si>
     <t>Non-Tariff Notifications : 2024</t>
   </si>
@@ -1158,7 +1158,10 @@
     <t>"Notification of ICD at Umarwada, Ankleshwar, Bharuch, Gujarat u/s. 7(1)(aa) of Customs Act, 1962" and it was issued under Section 7(1)(aa) of Customs Act, 1962.</t>
   </si>
   <si>
-    <t>69/2026-Customs (N.T)</t>
+    <t>69/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>70/2026-Customs (NT)</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1227,24 +1230,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="15" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1531,7 +1529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1566,728 +1564,739 @@
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>378</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B7" s="3">
         <v>46244</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="C7" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>375</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B8" s="3">
         <v>46234</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C8" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>376</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B9" s="3">
         <v>46234</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>373</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B10" s="3">
         <v>46223</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C10" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>369</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B11" s="3">
         <v>46219</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C11" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>371</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B12" s="3">
         <v>46219</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C12" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>372</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B13" s="3">
         <v>46218</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="C13" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B14" s="3">
         <v>46206</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C14" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>365</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B15" s="3">
         <v>46204</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>364</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B16" s="3">
         <v>46203</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="C16" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>363</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B17" s="3">
         <v>46202</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="C17" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>358</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B18" s="3">
         <v>46195</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>359</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B19" s="3">
         <v>46191</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C19" s="2" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>360</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B20" s="3">
         <v>46189</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C20" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>361</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B21" s="3">
         <v>46188</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="C21" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>354</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B22" s="3">
         <v>46184</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="C22" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>362</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B23" s="3">
         <v>46184</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C23" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>351</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B24" s="3">
         <v>46182</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C24" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>342</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B25" s="3">
         <v>46178</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C25" s="2" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>344</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B26" s="3">
         <v>46178</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C26" s="2" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>346</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B27" s="3">
         <v>46171</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C27" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>347</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B28" s="3">
         <v>46161</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="C28" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>348</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B29" s="3">
         <v>46157</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+      <c r="C29" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>349</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B30" s="3">
         <v>46150</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+      <c r="C30" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>350</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B31" s="3">
         <v>46148</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C31" s="2" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>320</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B32" s="3">
         <v>46142</v>
       </c>
-      <c r="C31" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+      <c r="C32" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>318</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B33" s="3">
         <v>46136</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C33" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>321</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B34" s="3">
         <v>46132</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C34" s="8" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>316</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B35" s="3">
         <v>46128</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C35" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>322</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B36" s="3">
         <v>46127</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+      <c r="C36" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>323</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B37" s="3">
         <v>46118</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C37" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>324</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B38" s="3">
         <v>46114</v>
       </c>
-      <c r="C37" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
+      <c r="C38" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>191</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B39" s="3">
         <v>46112</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C39" s="2" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>192</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B40" s="3">
         <v>46112</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C40" s="2" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>325</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B41" s="3">
         <v>46111</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C41" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>326</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B42" s="3">
         <v>46111</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C42" s="2" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>327</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B43" s="3">
         <v>46105</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C43" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>328</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B44" s="3">
         <v>46101</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C44" s="2" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>329</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B45" s="3">
         <v>46101</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C45" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>330</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B46" s="3">
         <v>46100</v>
       </c>
-      <c r="C45" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
+      <c r="C46" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>265</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B47" s="3">
         <v>46097</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C47" s="2" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>266</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B48" s="3">
         <v>46094</v>
       </c>
-      <c r="C47" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
+      <c r="C48" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>201</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B49" s="3">
         <v>46077</v>
       </c>
-      <c r="C48" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
+      <c r="C49" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>303</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B50" s="3">
         <v>46071</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
+      <c r="C50" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>304</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B51" s="3">
         <v>46069</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C51" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>305</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B52" s="3">
         <v>46066</v>
       </c>
-      <c r="C51" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
+      <c r="C52" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>306</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B53" s="3">
         <v>46059</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
+      <c r="C53" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>307</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B54" s="3">
         <v>46058</v>
       </c>
-      <c r="C53" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
+      <c r="C54" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>308</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B55" s="3">
         <v>46056</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+      <c r="C55" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B56" s="3">
         <v>46056</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C56" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>287</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B57" s="3">
         <v>46055</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
+      <c r="C57" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>288</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B58" s="3">
         <v>46054</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C58" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>290</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B59" s="3">
         <v>46054</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C59" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>292</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B60" s="3">
         <v>46054</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C60" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>294</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B61" s="3">
         <v>46054</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C61" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>296</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B62" s="3">
         <v>46052</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
+      <c r="C62" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>331</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B63" s="3">
         <v>46051</v>
       </c>
-      <c r="C62" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
+      <c r="C63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>332</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B64" s="3">
         <v>46049</v>
       </c>
-      <c r="C63" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="9" t="s">
+      <c r="C64" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>333</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B65" s="3">
         <v>46044</v>
       </c>
-      <c r="C64" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
+      <c r="C65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>334</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B66" s="3">
         <v>46037</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C66" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>335</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B67" s="3">
         <v>46037</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C67" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>336</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B68" s="3">
         <v>46037</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C68" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>337</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B69" s="3">
         <v>46037</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C69" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>338</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B70" s="3">
         <v>46037</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C70" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>339</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B71" s="3">
         <v>46037</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C71" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>340</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B72" s="3">
         <v>46035</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C72" t="s">
         <v>302</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A067E975-9B83-44E5-919B-4F79D764ECDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B23ADB-5BB6-4C62-B0EC-9858855B8BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="382">
   <si>
     <t>Non-Tariff Notifications : 2024</t>
   </si>
@@ -1140,9 +1140,6 @@
     <t>64/2026-Customs (NT)</t>
   </si>
   <si>
-    <t>63/2026-Customs (N.T)</t>
-  </si>
-  <si>
     <t>66/2026-Customs (NT)</t>
   </si>
   <si>
@@ -1162,6 +1159,15 @@
   </si>
   <si>
     <t>70/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>71/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>63/2026-Customs (NT)</t>
+  </si>
+  <si>
+    <t>Corrigendum to Tariff Notification No. 16/2026-Customs (NT) dated 2nd February, 2026</t>
   </si>
 </sst>
 </file>
@@ -1529,27 +1535,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C73"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.109375" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="149.42578125" customWidth="1"/>
+    <col min="3" max="3" width="149.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>285</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -1560,743 +1566,754 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>379</v>
       </c>
       <c r="B6" s="10">
-        <v>46248</v>
+        <v>46259</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>378</v>
       </c>
       <c r="B7" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B8" s="3">
         <v>46244</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>375</v>
-      </c>
-      <c r="B8" s="3">
-        <v>46234</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B9" s="3">
         <v>46234</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46234</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>372</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46223</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B10" s="3">
-        <v>46223</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>369</v>
-      </c>
-      <c r="B11" s="3">
-        <v>46219</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>371</v>
       </c>
       <c r="B12" s="3">
         <v>46219</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>371</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46219</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>372</v>
-      </c>
-      <c r="B13" s="3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>380</v>
+      </c>
+      <c r="B14" s="3">
         <v>46218</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="C14" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B15" s="3">
         <v>46206</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>365</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B16" s="3">
         <v>46204</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>364</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B17" s="3">
         <v>46203</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C17" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>363</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B18" s="3">
         <v>46202</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C18" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>358</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B19" s="3">
         <v>46195</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>359</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B20" s="3">
         <v>46191</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>360</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B21" s="3">
         <v>46189</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>361</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B22" s="3">
         <v>46188</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C22" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>354</v>
-      </c>
-      <c r="B22" s="3">
-        <v>46184</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>362</v>
       </c>
       <c r="B23" s="3">
         <v>46184</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>362</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46184</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="25" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>351</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B25" s="3">
         <v>46182</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="26" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>342</v>
-      </c>
-      <c r="B25" s="3">
-        <v>46178</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>344</v>
       </c>
       <c r="B26" s="3">
         <v>46178</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>344</v>
+      </c>
+      <c r="B27" s="3">
+        <v>46178</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>346</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B28" s="3">
         <v>46171</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>347</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <v>46161</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="C29" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>348</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>46157</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="C30" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>349</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <v>46150</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="C31" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>350</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B32" s="3">
         <v>46148</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>320</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B33" s="3">
         <v>46142</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="C33" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>318</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B34" s="3">
         <v>46136</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>321</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B35" s="3">
         <v>46132</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C35" s="8" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>316</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B36" s="3">
         <v>46128</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>322</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B37" s="3">
         <v>46127</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="C37" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>323</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B38" s="3">
         <v>46118</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>324</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B39" s="3">
         <v>46114</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="C39" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>191</v>
-      </c>
-      <c r="B39" s="3">
-        <v>46112</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>192</v>
       </c>
       <c r="B40" s="3">
         <v>46112</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="3">
+        <v>46112</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>325</v>
-      </c>
-      <c r="B41" s="3">
-        <v>46111</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>326</v>
       </c>
       <c r="B42" s="3">
         <v>46111</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>326</v>
+      </c>
+      <c r="B43" s="3">
+        <v>46111</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>327</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B44" s="3">
         <v>46105</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>328</v>
-      </c>
-      <c r="B44" s="3">
-        <v>46101</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>329</v>
       </c>
       <c r="B45" s="3">
         <v>46101</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>329</v>
+      </c>
+      <c r="B46" s="3">
+        <v>46101</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>330</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B47" s="3">
         <v>46100</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="C47" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>265</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B48" s="3">
         <v>46097</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>266</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B49" s="3">
         <v>46094</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="C49" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>201</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B50" s="3">
         <v>46077</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="C50" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>303</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B51" s="3">
         <v>46071</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="C51" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>304</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B52" s="3">
         <v>46069</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>305</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B53" s="3">
         <v>46066</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="C53" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>306</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B54" s="3">
         <v>46059</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="C54" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>307</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B55" s="3">
         <v>46058</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="C55" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>308</v>
-      </c>
-      <c r="B55" s="3">
-        <v>46056</v>
-      </c>
-      <c r="C55" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="B56" s="3">
         <v>46056</v>
       </c>
       <c r="C56" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B57" s="3">
+        <v>46056</v>
+      </c>
+      <c r="C57" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>287</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B58" s="3">
         <v>46055</v>
       </c>
-      <c r="C57" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="C58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>288</v>
-      </c>
-      <c r="B58" s="3">
-        <v>46054</v>
-      </c>
-      <c r="C58" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>290</v>
       </c>
       <c r="B59" s="3">
         <v>46054</v>
       </c>
       <c r="C59" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B60" s="3">
         <v>46054</v>
       </c>
       <c r="C60" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B61" s="3">
         <v>46054</v>
       </c>
       <c r="C61" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>294</v>
+      </c>
+      <c r="B62" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C62" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>296</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B63" s="3">
         <v>46052</v>
       </c>
-      <c r="C62" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="C63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>331</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B64" s="3">
         <v>46051</v>
       </c>
-      <c r="C63" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="C64" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>332</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B65" s="3">
         <v>46049</v>
       </c>
-      <c r="C64" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="C65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>333</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B66" s="3">
         <v>46044</v>
       </c>
-      <c r="C65" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="C66" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>334</v>
-      </c>
-      <c r="B66" s="3">
-        <v>46037</v>
-      </c>
-      <c r="C66" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>335</v>
       </c>
       <c r="B67" s="3">
         <v>46037</v>
       </c>
       <c r="C67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B68" s="3">
         <v>46037</v>
       </c>
       <c r="C68" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B69" s="3">
         <v>46037</v>
       </c>
       <c r="C69" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B70" s="3">
         <v>46037</v>
       </c>
       <c r="C70" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B71" s="3">
         <v>46037</v>
       </c>
       <c r="C71" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>339</v>
+      </c>
+      <c r="B72" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C72" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>340</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B73" s="3">
         <v>46035</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C73" t="s">
         <v>302</v>
       </c>
     </row>
@@ -2309,19 +2326,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E13EE4D-DCCA-4BD4-BA31-74C3648A2AB5}">
   <dimension ref="A1:C85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="142.28515625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="29.44140625" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="142.33203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -2332,7 +2349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>224</v>
       </c>
@@ -2343,7 +2360,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>225</v>
       </c>
@@ -2354,7 +2371,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>156</v>
       </c>
@@ -2365,7 +2382,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>226</v>
       </c>
@@ -2376,7 +2393,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>227</v>
       </c>
@@ -2387,7 +2404,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>228</v>
       </c>
@@ -2398,7 +2415,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>229</v>
       </c>
@@ -2409,7 +2426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>230</v>
       </c>
@@ -2420,7 +2437,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>158</v>
       </c>
@@ -2431,7 +2448,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>231</v>
       </c>
@@ -2442,7 +2459,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>232</v>
       </c>
@@ -2453,7 +2470,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>233</v>
       </c>
@@ -2464,7 +2481,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>234</v>
       </c>
@@ -2475,7 +2492,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>235</v>
       </c>
@@ -2486,7 +2503,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>236</v>
       </c>
@@ -2497,7 +2514,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>237</v>
       </c>
@@ -2508,7 +2525,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>165</v>
       </c>
@@ -2519,7 +2536,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>238</v>
       </c>
@@ -2530,7 +2547,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>239</v>
       </c>
@@ -2541,7 +2558,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>240</v>
       </c>
@@ -2552,7 +2569,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>241</v>
       </c>
@@ -2563,7 +2580,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>242</v>
       </c>
@@ -2574,7 +2591,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>243</v>
       </c>
@@ -2585,7 +2602,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>244</v>
       </c>
@@ -2596,7 +2613,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>245</v>
       </c>
@@ -2607,7 +2624,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>246</v>
       </c>
@@ -2618,7 +2635,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>247</v>
       </c>
@@ -2629,7 +2646,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>174</v>
       </c>
@@ -2640,7 +2657,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>248</v>
       </c>
@@ -2651,7 +2668,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>249</v>
       </c>
@@ -2662,7 +2679,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>250</v>
       </c>
@@ -2673,7 +2690,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>251</v>
       </c>
@@ -2684,7 +2701,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>252</v>
       </c>
@@ -2695,7 +2712,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>253</v>
       </c>
@@ -2706,7 +2723,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>254</v>
       </c>
@@ -2717,7 +2734,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>255</v>
       </c>
@@ -2728,7 +2745,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>256</v>
       </c>
@@ -2739,7 +2756,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>257</v>
       </c>
@@ -2750,7 +2767,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>258</v>
       </c>
@@ -2761,7 +2778,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>259</v>
       </c>
@@ -2772,7 +2789,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>183</v>
       </c>
@@ -2783,7 +2800,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>260</v>
       </c>
@@ -2794,7 +2811,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>185</v>
       </c>
@@ -2805,7 +2822,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>187</v>
       </c>
@@ -2816,7 +2833,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>189</v>
       </c>
@@ -2827,7 +2844,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>191</v>
       </c>
@@ -2838,7 +2855,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>192</v>
       </c>
@@ -2849,7 +2866,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>193</v>
       </c>
@@ -2860,7 +2877,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>261</v>
       </c>
@@ -2871,7 +2888,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>262</v>
       </c>
@@ -2882,7 +2899,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>196</v>
       </c>
@@ -2893,7 +2910,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>263</v>
       </c>
@@ -2904,7 +2921,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>264</v>
       </c>
@@ -2915,7 +2932,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>265</v>
       </c>
@@ -2926,7 +2943,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>266</v>
       </c>
@@ -2937,7 +2954,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>267</v>
       </c>
@@ -2948,7 +2965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>201</v>
       </c>
@@ -2959,7 +2976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>202</v>
       </c>
@@ -2970,7 +2987,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>204</v>
       </c>
@@ -2981,7 +2998,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>268</v>
       </c>
@@ -2992,7 +3009,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>269</v>
       </c>
@@ -3003,7 +3020,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>270</v>
       </c>
@@ -3014,7 +3031,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>209</v>
       </c>
@@ -3025,7 +3042,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>271</v>
       </c>
@@ -3036,7 +3053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>272</v>
       </c>
@@ -3047,7 +3064,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>273</v>
       </c>
@@ -3058,7 +3075,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>274</v>
       </c>
@@ -3069,7 +3086,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>275</v>
       </c>
@@ -3080,7 +3097,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>276</v>
       </c>
@@ -3091,7 +3108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>277</v>
       </c>
@@ -3102,7 +3119,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>278</v>
       </c>
@@ -3113,7 +3130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>214</v>
       </c>
@@ -3124,7 +3141,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>216</v>
       </c>
@@ -3135,7 +3152,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>218</v>
       </c>
@@ -3146,7 +3163,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>279</v>
       </c>
@@ -3157,7 +3174,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>280</v>
       </c>
@@ -3168,7 +3185,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>281</v>
       </c>
@@ -3179,7 +3196,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>282</v>
       </c>
@@ -3190,7 +3207,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>283</v>
       </c>
@@ -3201,7 +3218,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>284</v>
       </c>
@@ -3220,19 +3237,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B4A2D4A-A621-4ADC-A5B8-652ABC75FF05}">
   <dimension ref="A1:C93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="143.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="143.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -3243,7 +3260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3254,7 +3271,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -3265,7 +3282,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3276,7 +3293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>139</v>
       </c>
@@ -3287,7 +3304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>140</v>
       </c>
@@ -3298,7 +3315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -3309,7 +3326,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>151</v>
       </c>
@@ -3320,7 +3337,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -3331,7 +3348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -3342,7 +3359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -3353,7 +3370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -3364,7 +3381,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -3375,7 +3392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -3386,7 +3403,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -3397,7 +3414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>141</v>
       </c>
@@ -3408,7 +3425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -3419,7 +3436,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -3430,7 +3447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -3441,7 +3458,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3452,7 +3469,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3463,7 +3480,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -3474,7 +3491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -3485,7 +3502,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -3496,7 +3513,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -3507,7 +3524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -3518,7 +3535,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -3529,7 +3546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -3540,7 +3557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -3551,7 +3568,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -3562,7 +3579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -3573,7 +3590,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -3584,7 +3601,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>52</v>
       </c>
@@ -3595,7 +3612,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>54</v>
       </c>
@@ -3606,7 +3623,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -3617,7 +3634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>142</v>
       </c>
@@ -3628,7 +3645,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -3639,7 +3656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -3650,7 +3667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -3661,7 +3678,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>62</v>
       </c>
@@ -3672,7 +3689,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>64</v>
       </c>
@@ -3683,7 +3700,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>143</v>
       </c>
@@ -3694,7 +3711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>66</v>
       </c>
@@ -3705,7 +3722,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>68</v>
       </c>
@@ -3716,7 +3733,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>70</v>
       </c>
@@ -3727,7 +3744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>144</v>
       </c>
@@ -3738,7 +3755,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>72</v>
       </c>
@@ -3749,7 +3766,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -3760,7 +3777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -3771,7 +3788,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>145</v>
       </c>
@@ -3782,7 +3799,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>146</v>
       </c>
@@ -3793,7 +3810,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>147</v>
       </c>
@@ -3804,7 +3821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>79</v>
       </c>
@@ -3815,7 +3832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>148</v>
       </c>
@@ -3826,7 +3843,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>81</v>
       </c>
@@ -3837,7 +3854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>149</v>
       </c>
@@ -3848,7 +3865,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>150</v>
       </c>
@@ -3859,7 +3876,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>137</v>
       </c>
@@ -3870,7 +3887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>84</v>
       </c>
@@ -3881,7 +3898,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -3892,7 +3909,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>88</v>
       </c>
@@ -3903,7 +3920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>136</v>
       </c>
@@ -3914,7 +3931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>89</v>
       </c>
@@ -3925,7 +3942,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>135</v>
       </c>
@@ -3936,7 +3953,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>134</v>
       </c>
@@ -3947,7 +3964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>92</v>
       </c>
@@ -3958,7 +3975,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>94</v>
       </c>
@@ -3969,7 +3986,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>96</v>
       </c>
@@ -3980,7 +3997,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>98</v>
       </c>
@@ -3991,7 +4008,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>100</v>
       </c>
@@ -4002,7 +4019,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>102</v>
       </c>
@@ -4013,7 +4030,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -4024,7 +4041,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>106</v>
       </c>
@@ -4035,7 +4052,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>107</v>
       </c>
@@ -4046,7 +4063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>133</v>
       </c>
@@ -4057,7 +4074,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>109</v>
       </c>
@@ -4068,7 +4085,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>111</v>
       </c>
@@ -4079,7 +4096,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>113</v>
       </c>
@@ -4090,7 +4107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>114</v>
       </c>
@@ -4101,7 +4118,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>116</v>
       </c>
@@ -4112,7 +4129,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>118</v>
       </c>
@@ -4123,7 +4140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>119</v>
       </c>
@@ -4134,7 +4151,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>121</v>
       </c>
@@ -4145,7 +4162,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>123</v>
       </c>
@@ -4156,7 +4173,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>125</v>
       </c>
@@ -4167,7 +4184,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>152</v>
       </c>
@@ -4178,7 +4195,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>132</v>
       </c>
@@ -4189,7 +4206,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>129</v>
       </c>
@@ -4200,7 +4217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>130</v>
       </c>

--- a/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Non-Tariff/Non-Tariff Notifications.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B23ADB-5BB6-4C62-B0EC-9858855B8BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB3FAEF-A1A6-4544-8695-21AF6EA1EA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="383">
   <si>
     <t>Non-Tariff Notifications : 2024</t>
   </si>
@@ -1168,6 +1168,9 @@
   </si>
   <si>
     <t>Corrigendum to Tariff Notification No. 16/2026-Customs (NT) dated 2nd February, 2026</t>
+  </si>
+  <si>
+    <t>72/2026-Customs (NT)</t>
   </si>
 </sst>
 </file>
@@ -1535,7 +1538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.109375" customWidth="1"/>
@@ -1571,10 +1574,10 @@
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B6" s="10">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>154</v>
@@ -1582,10 +1585,10 @@
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B7" s="3">
-        <v>46248</v>
+        <v>46259</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>154</v>
@@ -1593,120 +1596,120 @@
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>377</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B9" s="3">
         <v>46244</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>374</v>
-      </c>
-      <c r="B9" s="3">
-        <v>46234</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B10" s="3">
         <v>46234</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>376</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>375</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46234</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>372</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B12" s="3">
         <v>46223</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>369</v>
-      </c>
-      <c r="B12" s="3">
-        <v>46219</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>371</v>
       </c>
       <c r="B13" s="3">
         <v>46219</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>163</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>371</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46219</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>380</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B15" s="3">
         <v>46218</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="C15" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B16" s="3">
         <v>46206</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>365</v>
-      </c>
-      <c r="B16" s="3">
-        <v>46204</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B17" s="3">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>154</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B18" s="3">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>154</v>
@@ -1714,131 +1717,131 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B19" s="3">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>357</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B20" s="3">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B21" s="3">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B22" s="3">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>154</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>361</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46188</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>354</v>
-      </c>
-      <c r="B23" s="3">
-        <v>46184</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>362</v>
       </c>
       <c r="B24" s="3">
         <v>46184</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>362</v>
+      </c>
+      <c r="B25" s="3">
+        <v>46184</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>355</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>351</v>
-      </c>
-      <c r="B25" s="3">
-        <v>46182</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B26" s="3">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B27" s="3">
         <v>46178</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>344</v>
+      </c>
+      <c r="B28" s="3">
+        <v>46178</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>346</v>
-      </c>
-      <c r="B28" s="3">
-        <v>46171</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B29" s="3">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B30" s="3">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>154</v>
@@ -1846,10 +1849,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B31" s="3">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>154</v>
@@ -1857,208 +1860,208 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B32" s="3">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>341</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="B33" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>154</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B34" s="3">
-        <v>46136</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>163</v>
+        <v>46142</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>318</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46136</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>321</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B36" s="3">
         <v>46132</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>316</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B37" s="3">
         <v>46128</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>317</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>322</v>
-      </c>
-      <c r="B37" s="3">
-        <v>46127</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B38" s="3">
-        <v>46118</v>
+        <v>46127</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>315</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B39" s="3">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>154</v>
+        <v>315</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>324</v>
       </c>
       <c r="B40" s="3">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>311</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B41" s="3">
         <v>46112</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>325</v>
+        <v>192</v>
       </c>
       <c r="B42" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B43" s="3">
         <v>46111</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>313</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B44" s="3">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B45" s="3">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B46" s="3">
         <v>46101</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>171</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B47" s="3">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>265</v>
+        <v>330</v>
       </c>
       <c r="B48" s="3">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>310</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B49" s="3">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>154</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="B50" s="3">
-        <v>46077</v>
+        <v>46094</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>154</v>
@@ -2066,43 +2069,43 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" s="3">
+        <v>46077</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>303</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B52" s="3">
         <v>46071</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="C52" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>304</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B53" s="3">
         <v>46069</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>305</v>
-      </c>
-      <c r="B53" s="3">
-        <v>46066</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B54" s="3">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>154</v>
@@ -2110,10 +2113,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B55" s="3">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>154</v>
@@ -2121,98 +2124,98 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>307</v>
+      </c>
+      <c r="B56" s="3">
+        <v>46058</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>308</v>
-      </c>
-      <c r="B56" s="3">
-        <v>46056</v>
-      </c>
-      <c r="C56" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="B57" s="3">
         <v>46056</v>
       </c>
       <c r="C57" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B58" s="3">
+        <v>46056</v>
+      </c>
+      <c r="C58" t="s">
         <v>286</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>287</v>
-      </c>
-      <c r="B58" s="3">
-        <v>46055</v>
-      </c>
-      <c r="C58" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B59" s="3">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C59" t="s">
-        <v>289</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B60" s="3">
         <v>46054</v>
       </c>
       <c r="C60" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B61" s="3">
         <v>46054</v>
       </c>
       <c r="C61" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B62" s="3">
         <v>46054</v>
       </c>
       <c r="C62" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B63" s="3">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="C63" t="s">
-        <v>154</v>
+        <v>295</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="B64" s="3">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="C64" t="s">
         <v>154</v>
@@ -2220,10 +2223,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B65" s="3">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="C65" t="s">
         <v>154</v>
@@ -2231,10 +2234,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B66" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="C66" t="s">
         <v>154</v>
@@ -2242,78 +2245,89 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B67" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="C67" t="s">
-        <v>297</v>
+        <v>154</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B68" s="3">
         <v>46037</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B69" s="3">
         <v>46037</v>
       </c>
       <c r="C69" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B70" s="3">
         <v>46037</v>
       </c>
       <c r="C70" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B71" s="3">
         <v>46037</v>
       </c>
       <c r="C71" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B72" s="3">
         <v>46037</v>
       </c>
       <c r="C72" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>339</v>
+      </c>
+      <c r="B73" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C73" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>340</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B74" s="3">
         <v>46035</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C74" t="s">
         <v>302</v>
       </c>
     </row>
